--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -911,19 +911,19 @@
         <v>-75</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
         <v>-66.666666666666</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="15">
         <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>-23.076923076923</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L16" s="14">
         <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-72.222222222222</v>
+        <v>-71.794871794871</v>
       </c>
       <c r="N16" s="14">
-        <v>-96.124031007751</v>
+        <v>-96.369636963696</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-70</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-37.931034482758</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I17" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M17" s="14">
-        <v>15.384615384615</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="14">
         <v>-71.428571428571</v>
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-41.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-55</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-71.875</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.267515923566</v>
+        <v>-92.349726775956</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" s="14">
-        <v>-4.545454545454</v>
+        <v>-10</v>
       </c>
       <c r="I19" s="15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J19" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.216216216216</v>
+        <v>-7.5</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.428571428571</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="M19" s="14">
-        <v>14.814814814814</v>
+        <v>15.625</v>
       </c>
       <c r="N19" s="14">
-        <v>-49.180327868852</v>
+        <v>-45.588235294117</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J20" s="15">
         <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L20" s="14">
-        <v>-21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>-21.428571428571</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N20" s="14">
-        <v>-87.640449438202</v>
+        <v>-86.363636363636</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.75</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="I21" s="17">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="J21" s="17">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.770491803278</v>
+        <v>-16.546762589928</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.140495867768</v>
+        <v>-18.881118881118</v>
       </c>
       <c r="M21" s="18">
-        <v>-32.608695652173</v>
+        <v>-25.161290322580</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.521739130434</v>
+        <v>-85.766871165644</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
         <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
+        <v>12</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I23" s="15">
         <v>10</v>
       </c>
-      <c r="H23" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I23" s="15">
-        <v>7</v>
-      </c>
       <c r="J23" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K23" s="14">
-        <v>-53.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L23" s="14">
-        <v>-30</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
         <v>11</v>
       </c>
       <c r="E24" s="14">
-        <v>27.272727272727</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F24" s="15">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14">
-        <v>-6.557377049180</v>
+        <v>10.909090909090</v>
       </c>
       <c r="I24" s="15">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J24" s="15">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.730337078651</v>
+        <v>-6</v>
       </c>
       <c r="L24" s="14">
-        <v>-1.315789473684</v>
+        <v>2.173913043478</v>
       </c>
       <c r="M24" s="14">
-        <v>-11.764705882352</v>
+        <v>-3.092783505154</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,7 +1303,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1312,25 +1312,25 @@
         <v>21</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="I25" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J25" s="15">
         <v>6</v>
       </c>
       <c r="K25" s="14">
-        <v>133.333333333333</v>
+        <v>216.666666666667</v>
       </c>
       <c r="L25" s="14">
-        <v>7.692307692307</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>166.666666666667</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>4.166666666666</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J26" s="15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K26" s="14">
-        <v>26.666666666666</v>
+        <v>22.5</v>
       </c>
       <c r="L26" s="14">
-        <v>-5</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M26" s="14">
-        <v>-50.649350649350</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>-80</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
         <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="14">
         <v>28.571428571428</v>
-      </c>
-      <c r="L28" s="14">
-        <v>80</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="L14" s="14">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
+      <c r="H15" s="14">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
         <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-75</v>
-      </c>
-      <c r="I15" s="15">
-        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>6</v>
-      </c>
       <c r="E16" s="14">
-        <v>-83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>-42.105263157894</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-71.794871794871</v>
+        <v>-67.441860465116</v>
       </c>
       <c r="N16" s="14">
-        <v>-96.369636963696</v>
+        <v>-95.770392749244</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <v>18</v>
+      </c>
+      <c r="G17" s="15">
+        <v>30</v>
+      </c>
+      <c r="H17" s="14">
         <v>-40</v>
       </c>
-      <c r="F17" s="15">
-        <v>15</v>
-      </c>
-      <c r="G17" s="15">
-        <v>27</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-44.444444444444</v>
-      </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J17" s="15">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>-20</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L17" s="14">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-71.428571428571</v>
+        <v>-70.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="14">
-        <v>-33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="14">
-        <v>-61.111111111111</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.349726775956</v>
+        <v>-91.219512195122</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15">
         <v>6</v>
       </c>
-      <c r="D19" s="15">
-        <v>3</v>
-      </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
-        <v>-10</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I19" s="15">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J19" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.5</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.953488372093</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="M19" s="14">
-        <v>15.625</v>
+        <v>26.470588235294</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.588235294117</v>
+        <v>-47.560975609756</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>50</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L20" s="14">
+        <v>20</v>
+      </c>
+      <c r="M20" s="14">
         <v>0</v>
       </c>
-      <c r="M20" s="14">
-        <v>-11.764705882352</v>
-      </c>
       <c r="N20" s="14">
-        <v>-86.363636363636</v>
+        <v>-86.466165413533</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
         <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.368421052631</v>
+        <v>-5.479452054794</v>
       </c>
       <c r="I21" s="17">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="J21" s="17">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.546762589928</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.881118881118</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.161290322580</v>
+        <v>-18.497109826589</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.766871165644</v>
+        <v>-84.789644012945</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
-      </c>
-      <c r="D23" s="15">
-        <v>3</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>8</v>
       </c>
       <c r="G23" s="15">
+        <v>10</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-20</v>
+      </c>
+      <c r="I23" s="15">
         <v>12</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I23" s="15">
-        <v>10</v>
       </c>
       <c r="J23" s="15">
         <v>18</v>
       </c>
       <c r="K23" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>72.727272727272</v>
+        <v>87.5</v>
       </c>
       <c r="F24" s="15">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G24" s="15">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H24" s="14">
-        <v>10.909090909090</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I24" s="15">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="J24" s="15">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K24" s="14">
-        <v>-6</v>
+        <v>1.851851851851</v>
       </c>
       <c r="L24" s="14">
-        <v>2.173913043478</v>
+        <v>6.796116504854</v>
       </c>
       <c r="M24" s="14">
-        <v>-3.092783505154</v>
+        <v>2.803738317757</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="14">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="I25" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J25" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K25" s="14">
-        <v>216.666666666667</v>
+        <v>175</v>
       </c>
       <c r="L25" s="14">
-        <v>35.714285714285</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.448275862068</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="15">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J26" s="15">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K26" s="14">
-        <v>22.5</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.921568627450</v>
+        <v>1.694915254237</v>
       </c>
       <c r="M26" s="14">
-        <v>-41.666666666666</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>5</v>
-      </c>
       <c r="H27" s="14">
-        <v>-80</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="14">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,284 +854,284 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="14">
+      <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="N14" s="14">
+      <c r="M14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="15">
+        <v>21</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
+        <v>200</v>
+      </c>
+      <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
+        <v>4</v>
+      </c>
+      <c r="K15" s="15">
+        <v>50</v>
+      </c>
+      <c r="L15" s="15">
         <v>100</v>
       </c>
-      <c r="I15" s="15">
-        <v>4</v>
-      </c>
-      <c r="J15" s="15">
-        <v>4</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="M15" s="15">
         <v>100</v>
       </c>
-      <c r="M15" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-55.555555555555</v>
+      <c r="N15" s="15">
+        <v>-45.454545454545</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>9</v>
-      </c>
-      <c r="G16" s="15">
-        <v>9</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="E16" s="15">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>11</v>
+      </c>
+      <c r="G16" s="14">
+        <v>11</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="15">
-        <v>14</v>
-      </c>
-      <c r="J16" s="15">
-        <v>20</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-30</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-67.441860465116</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-95.770392749244</v>
+      <c r="I16" s="14">
+        <v>17</v>
+      </c>
+      <c r="J16" s="14">
+        <v>22</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-22.727272727272</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-39.285714285714</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-63.829787234042</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-95.417789757412</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>8</v>
-      </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
-      <c r="E17" s="14">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <v>18</v>
-      </c>
-      <c r="G17" s="15">
-        <v>30</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-40</v>
-      </c>
-      <c r="I17" s="15">
-        <v>44</v>
-      </c>
-      <c r="J17" s="15">
-        <v>53</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-16.981132075471</v>
-      </c>
-      <c r="L17" s="14">
-        <v>0</v>
-      </c>
-      <c r="M17" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-70.666666666666</v>
+      <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
+        <v>11</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-63.636363636363</v>
+      </c>
+      <c r="F17" s="14">
+        <v>19</v>
+      </c>
+      <c r="G17" s="14">
+        <v>34</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-44.117647058823</v>
+      </c>
+      <c r="I17" s="14">
+        <v>48</v>
+      </c>
+      <c r="J17" s="14">
+        <v>64</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-2.040816326530</v>
+      </c>
+      <c r="M17" s="15">
+        <v>23.076923076923</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-72.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>4</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>300</v>
-      </c>
-      <c r="F18" s="15">
-        <v>11</v>
-      </c>
-      <c r="G18" s="15">
-        <v>11</v>
-      </c>
-      <c r="H18" s="14">
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
         <v>0</v>
       </c>
-      <c r="I18" s="15">
-        <v>18</v>
-      </c>
-      <c r="J18" s="15">
-        <v>22</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-53.846153846153</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-91.219512195122</v>
+      <c r="F18" s="14">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="15">
+        <v>25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>21</v>
+      </c>
+      <c r="J18" s="14">
+        <v>24</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-16</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-52.272727272727</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-91.213389121338</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>5</v>
-      </c>
-      <c r="D19" s="15">
-        <v>6</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="F19" s="15">
-        <v>19</v>
-      </c>
-      <c r="G19" s="15">
-        <v>21</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-9.523809523809</v>
-      </c>
-      <c r="I19" s="15">
-        <v>43</v>
-      </c>
-      <c r="J19" s="15">
-        <v>46</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-6.521739130434</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-15.686274509803</v>
-      </c>
-      <c r="M19" s="14">
-        <v>26.470588235294</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-47.560975609756</v>
+      <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
+        <v>3</v>
+      </c>
+      <c r="E19" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="F19" s="14">
+        <v>24</v>
+      </c>
+      <c r="G19" s="14">
+        <v>16</v>
+      </c>
+      <c r="H19" s="15">
+        <v>50</v>
+      </c>
+      <c r="I19" s="14">
+        <v>50</v>
+      </c>
+      <c r="J19" s="14">
+        <v>49</v>
+      </c>
+      <c r="K19" s="15">
+        <v>2.040816326530</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-18.032786885245</v>
+      </c>
+      <c r="M19" s="15">
+        <v>31.578947368421</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>13</v>
+      </c>
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>200</v>
-      </c>
-      <c r="F20" s="15">
-        <v>10</v>
-      </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="14">
-        <v>900</v>
-      </c>
-      <c r="I20" s="15">
-        <v>18</v>
-      </c>
-      <c r="J20" s="15">
-        <v>11</v>
-      </c>
-      <c r="K20" s="14">
-        <v>63.636363636363</v>
-      </c>
-      <c r="L20" s="14">
-        <v>20</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-86.466165413533</v>
+      <c r="H20" s="15">
+        <v>333.333333333333</v>
+      </c>
+      <c r="I20" s="14">
+        <v>21</v>
+      </c>
+      <c r="J20" s="14">
+        <v>13</v>
+      </c>
+      <c r="K20" s="15">
+        <v>61.538461538461</v>
+      </c>
+      <c r="L20" s="15">
+        <v>23.529411764705</v>
+      </c>
+      <c r="M20" s="15">
+        <v>5</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-86</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,409 +1139,409 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>35.294117647058</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.479452054794</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I21" s="17">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="J21" s="17">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.615384615384</v>
+        <v>-7.909604519774</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.320754716981</v>
+        <v>-12.365591397849</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.497109826589</v>
+        <v>-15.979381443299</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.789644012945</v>
+        <v>-84.549763033175</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="15">
+        <v>22</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="H22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="15">
-        <v>2</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="14">
         <v>3</v>
       </c>
-      <c r="K22" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-60</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-71.428571428571</v>
+      <c r="J22" s="14">
+        <v>3</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="14">
+        <v>3</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
-        <v>8</v>
-      </c>
-      <c r="G23" s="15">
-        <v>10</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I23" s="15">
-        <v>12</v>
-      </c>
-      <c r="J23" s="15">
+        <v>22</v>
+      </c>
+      <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="15">
+        <v>50</v>
+      </c>
+      <c r="I23" s="14">
+        <v>15</v>
+      </c>
+      <c r="J23" s="14">
         <v>18</v>
       </c>
-      <c r="K23" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="M23" s="14">
+      <c r="K23" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
         <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>15</v>
-      </c>
-      <c r="D24" s="15">
-        <v>8</v>
-      </c>
-      <c r="E24" s="14">
-        <v>87.5</v>
-      </c>
-      <c r="F24" s="15">
-        <v>58</v>
-      </c>
-      <c r="G24" s="15">
-        <v>44</v>
-      </c>
-      <c r="H24" s="14">
-        <v>31.818181818181</v>
-      </c>
-      <c r="I24" s="15">
-        <v>110</v>
-      </c>
-      <c r="J24" s="15">
-        <v>108</v>
-      </c>
-      <c r="K24" s="14">
-        <v>1.851851851851</v>
-      </c>
-      <c r="L24" s="14">
-        <v>6.796116504854</v>
-      </c>
-      <c r="M24" s="14">
-        <v>2.803738317757</v>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>7</v>
+      </c>
+      <c r="E24" s="15">
+        <v>185.714285714286</v>
+      </c>
+      <c r="F24" s="14">
+        <v>70</v>
+      </c>
+      <c r="G24" s="14">
+        <v>37</v>
+      </c>
+      <c r="H24" s="15">
+        <v>89.189189189189</v>
+      </c>
+      <c r="I24" s="14">
+        <v>131</v>
+      </c>
+      <c r="J24" s="14">
+        <v>115</v>
+      </c>
+      <c r="K24" s="15">
+        <v>13.913043478260</v>
+      </c>
+      <c r="L24" s="15">
+        <v>11.016949152542</v>
+      </c>
+      <c r="M24" s="15">
+        <v>12.931034482758</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>2</v>
-      </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
-      <c r="E25" s="14">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15">
-        <v>18</v>
-      </c>
-      <c r="G25" s="15">
-        <v>2</v>
-      </c>
-      <c r="H25" s="14">
-        <v>800</v>
-      </c>
-      <c r="I25" s="15">
-        <v>22</v>
-      </c>
-      <c r="J25" s="15">
-        <v>8</v>
-      </c>
-      <c r="K25" s="14">
-        <v>175</v>
-      </c>
-      <c r="L25" s="14">
-        <v>15.789473684210</v>
+      <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F25" s="14">
+        <v>20</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="15">
+        <v>300</v>
+      </c>
+      <c r="I25" s="14">
+        <v>27</v>
+      </c>
+      <c r="J25" s="14">
+        <v>11</v>
+      </c>
+      <c r="K25" s="15">
+        <v>145.454545454545</v>
+      </c>
+      <c r="L25" s="15">
+        <v>22.727272727272</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>11</v>
-      </c>
-      <c r="D26" s="15">
-        <v>11</v>
-      </c>
-      <c r="E26" s="14">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15">
-        <v>36</v>
-      </c>
-      <c r="G26" s="15">
-        <v>32</v>
-      </c>
-      <c r="H26" s="14">
-        <v>12.5</v>
-      </c>
-      <c r="I26" s="15">
-        <v>60</v>
-      </c>
-      <c r="J26" s="15">
-        <v>51</v>
-      </c>
-      <c r="K26" s="14">
-        <v>17.647058823529</v>
-      </c>
-      <c r="L26" s="14">
-        <v>1.694915254237</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-38.775510204081</v>
+      <c r="C26" s="14">
+        <v>9</v>
+      </c>
+      <c r="D26" s="14">
+        <v>3</v>
+      </c>
+      <c r="E26" s="15">
+        <v>200</v>
+      </c>
+      <c r="F26" s="14">
+        <v>39</v>
+      </c>
+      <c r="G26" s="14">
+        <v>27</v>
+      </c>
+      <c r="H26" s="15">
+        <v>44.444444444444</v>
+      </c>
+      <c r="I26" s="14">
+        <v>68</v>
+      </c>
+      <c r="J26" s="14">
+        <v>54</v>
+      </c>
+      <c r="K26" s="15">
+        <v>25.925925925925</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-8.108108108108</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-37.614678899082</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>100</v>
-      </c>
-      <c r="I27" s="15">
-        <v>4</v>
-      </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-20</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-42.857142857142</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
+        <v>7</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="15">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="F28" s="14">
         <v>5</v>
       </c>
-      <c r="H28" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I28" s="15">
-        <v>11</v>
-      </c>
-      <c r="J28" s="15">
-        <v>11</v>
-      </c>
-      <c r="K28" s="14">
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
+        <v>12</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="14">
-        <v>57.142857142857</v>
+      <c r="L28" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="15">
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="15">
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="H29" s="14">
+      <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="I29" s="15">
-        <v>1</v>
-      </c>
-      <c r="J29" s="15">
-        <v>1</v>
-      </c>
-      <c r="K29" s="14">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="14">
-        <v>-88.888888888888</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-97.560975609756</v>
+      <c r="L29" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M29" s="15">
+        <v>-90</v>
+      </c>
+      <c r="N29" s="15">
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="15">
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="15">
+      <c r="J30" s="14">
         <v>1</v>
       </c>
-      <c r="H30" s="14">
+      <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="I30" s="15">
-        <v>1</v>
-      </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="K30" s="14">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="14">
-        <v>-83.333333333333</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-97.435897435897</v>
+      <c r="L30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M30" s="15">
+        <v>-85.714285714285</v>
+      </c>
+      <c r="N30" s="15">
+        <v>-97.916666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1742,63 +1742,63 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>70</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>82</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>9</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>19</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>5</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-73.684210526315</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-44.444444444444</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-93.902439024390</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-92.857142857142</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="15">
+        <v>21</v>
+      </c>
+      <c r="C40" s="14">
         <v>99</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>71</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>52</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>43</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>25</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-41.860465116279</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-51.923076923076</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-64.788732394366</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-74.747474747474</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>2412</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>2202</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>772</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>487</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>182</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-62.628336755646</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-76.424870466321</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-91.734786557674</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-92.454394693200</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>1307</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>1190</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>648</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>498</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>460</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>-7.630522088353</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-29.012345679012</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-61.344537815126</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-64.804896710023</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2130</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1582</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>722</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>575</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>152</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-73.565217391304</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-78.947368421052</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-90.391908975979</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-92.863849765258</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>705</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>599</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>346</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>387</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>453</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>17.054263565891</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>30.924855491329</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-24.373956594323</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-35.744680851063</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1242</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>774</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>291</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>347</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>113</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-67.435158501440</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-61.168384879725</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-85.400516795865</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-90.901771336553</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>2</v>
@@ -899,34 +899,34 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>200</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-45.454545454545</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="15">
-        <v>50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
         <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.727272727272</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.285714285714</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.829787234042</v>
+        <v>-62</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.417789757412</v>
+        <v>-95.581395348837</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-63.636363636363</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-44.117647058823</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K17" s="15">
-        <v>-25</v>
+        <v>-15.942028985507</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.040816326530</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>23.076923076923</v>
+        <v>45</v>
       </c>
       <c r="N17" s="15">
-        <v>-72.571428571428</v>
+        <v>-69.148936170212</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.5</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-16</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.272727272727</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.213389121338</v>
+        <v>-92.114695340501</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>133.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="15">
-        <v>50</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I19" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K19" s="15">
-        <v>2.040816326530</v>
+        <v>1.851851851851</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.032786885245</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="M19" s="15">
-        <v>31.578947368421</v>
+        <v>30.952380952381</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.444444444444</v>
+        <v>-45.544554455445</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>333.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="14">
         <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>61.538461538461</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L20" s="15">
-        <v>23.529411764705</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M20" s="15">
-        <v>5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="N20" s="15">
-        <v>-86</v>
+        <v>-86.503067484662</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.761904761904</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>8.108108108108</v>
+        <v>20.289855072463</v>
       </c>
       <c r="I21" s="17">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.909604519774</v>
+        <v>-3.664921465968</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.365591397849</v>
+        <v>-10.679611650485</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.979381443299</v>
+        <v>-12.796208530805</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.549763033175</v>
+        <v>-84.550797649034</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="C23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>22</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.666666666666</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>185.714285714286</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H24" s="15">
-        <v>89.189189189189</v>
+        <v>53.191489361702</v>
       </c>
       <c r="I24" s="14">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="J24" s="14">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="K24" s="15">
-        <v>13.913043478260</v>
+        <v>8.088235294117</v>
       </c>
       <c r="L24" s="15">
-        <v>11.016949152542</v>
+        <v>8.088235294117</v>
       </c>
       <c r="M24" s="15">
-        <v>12.931034482758</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="15">
-        <v>145.454545454545</v>
+        <v>115.384615384615</v>
       </c>
       <c r="L25" s="15">
-        <v>22.727272727272</v>
+        <v>12</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>44.444444444444</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J26" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>25.925925925925</v>
+        <v>15.625</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.108108108108</v>
+        <v>-10.843373493975</v>
       </c>
       <c r="M26" s="15">
-        <v>-37.614678899082</v>
+        <v>-40.8</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,38 +1387,38 @@
       <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,7 +1473,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.039215686274</v>
+        <v>-98.076923076923</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,7 +1514,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1523,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.916666666666</v>
+        <v>-97.959183673469</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>99</v>

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
         <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.636363636363</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.709677419354</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="M16" s="15">
-        <v>-62</v>
+        <v>-58.181818181818</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.581395348837</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.793103448275</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.942028985507</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L17" s="15">
-        <v>3.571428571428</v>
+        <v>10.344827586206</v>
       </c>
       <c r="M17" s="15">
-        <v>45</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.148936170212</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.428571428571</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.137931034482</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.692307692307</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.114695340501</v>
+        <v>-92.207792207792</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="F19" s="14">
+        <v>25</v>
+      </c>
+      <c r="G19" s="14">
+        <v>25</v>
+      </c>
+      <c r="H19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="14">
-        <v>23</v>
-      </c>
-      <c r="G19" s="14">
-        <v>17</v>
-      </c>
-      <c r="H19" s="15">
-        <v>35.294117647058</v>
-      </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>1.851851851851</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.910447761194</v>
+        <v>-17.105263157894</v>
       </c>
       <c r="M19" s="15">
-        <v>30.952380952381</v>
+        <v>46.511627906976</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.544554455445</v>
+        <v>-42.727272727272</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
         <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>69.230769230769</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L20" s="15">
-        <v>29.411764705882</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>4.761904761904</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.503067484662</v>
+        <v>-86.592178770949</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>20.289855072463</v>
+        <v>14.473684210526</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="J21" s="17">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.664921465968</v>
+        <v>-4.186046511627</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.679611650485</v>
+        <v>-8.035714285714</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.796208530805</v>
+        <v>-11.206896551724</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.550797649034</v>
+        <v>-84.006211180124</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
         <v>-66.666666666666</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>140</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>-5</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>11.764705882352</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M23" s="15">
-        <v>72.727272727272</v>
+        <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-19.047619047619</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H24" s="15">
-        <v>53.191489361702</v>
+        <v>29.090909090909</v>
       </c>
       <c r="I24" s="14">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J24" s="14">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="K24" s="15">
-        <v>8.088235294117</v>
+        <v>7.096774193548</v>
       </c>
       <c r="L24" s="15">
-        <v>8.088235294117</v>
+        <v>12.925170068027</v>
       </c>
       <c r="M24" s="15">
-        <v>16.666666666666</v>
+        <v>16.083916083916</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
+        <v>9</v>
+      </c>
+      <c r="G25" s="14">
+        <v>8</v>
+      </c>
+      <c r="H25" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="I25" s="14">
+        <v>29</v>
+      </c>
+      <c r="J25" s="14">
         <v>14</v>
       </c>
-      <c r="G25" s="14">
-        <v>7</v>
-      </c>
-      <c r="H25" s="15">
-        <v>100</v>
-      </c>
-      <c r="I25" s="14">
-        <v>28</v>
-      </c>
-      <c r="J25" s="14">
-        <v>13</v>
-      </c>
       <c r="K25" s="15">
-        <v>115.384615384615</v>
+        <v>107.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>12</v>
+        <v>11.538461538461</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
         <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
         <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>5.882352941176</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I26" s="14">
+        <v>81</v>
+      </c>
+      <c r="J26" s="14">
         <v>74</v>
       </c>
-      <c r="J26" s="14">
-        <v>64</v>
-      </c>
       <c r="K26" s="15">
-        <v>15.625</v>
+        <v>9.459459459459</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.843373493975</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M26" s="15">
-        <v>-40.8</v>
+        <v>-41.726618705036</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,22 +1394,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>55.555555555555</v>
+        <v>70</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="H29" s="15">
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-90.909090909090</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.076923076923</v>
+        <v>-96.226415094339</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="H30" s="15">
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-87.5</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.959183673469</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -920,13 +920,13 @@
         <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>57.142857142857</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.538461538461</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.303030303030</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.181818181818</v>
+        <v>-50.877192982456</v>
       </c>
       <c r="N16" s="15">
-        <v>-95</v>
+        <v>-94.331983805668</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.677419354838</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J17" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.789473684210</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="L17" s="15">
-        <v>10.344827586206</v>
+        <v>12.698412698412</v>
       </c>
       <c r="M17" s="15">
-        <v>33.333333333333</v>
+        <v>29.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>-68</v>
+        <v>-68.161434977578</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="14">
         <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.580645161290</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.142857142857</v>
+        <v>-63.076923076923</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.207792207792</v>
+        <v>-92.705167173252</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>-87.5</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I19" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.076923076923</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.105263157894</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M19" s="15">
-        <v>46.511627906976</v>
+        <v>39.130434782608</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.727272727272</v>
+        <v>-48.387096774193</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>6</v>
+      </c>
+      <c r="G20" s="14">
         <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
-        <v>9</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
       </c>
       <c r="H20" s="15">
         <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
         <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>84.615384615384</v>
+        <v>92.307692307692</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>19.047619047619</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.592178770949</v>
+        <v>-87.309644670050</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
         <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>14.473684210526</v>
+        <v>2.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="J21" s="17">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.186046511627</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.035714285714</v>
+        <v>-10.931174089068</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.206896551724</v>
+        <v>-14.728682170542</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.006211180124</v>
+        <v>-84.274481772694</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-75</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
         <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>83.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
         <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.5</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>23.529411764705</v>
+        <v>10</v>
       </c>
       <c r="M23" s="15">
-        <v>75</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.263157894736</v>
+        <v>155.555555555556</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>29.090909090909</v>
+        <v>39.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="J24" s="14">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="K24" s="15">
-        <v>7.096774193548</v>
+        <v>15.243902439024</v>
       </c>
       <c r="L24" s="15">
-        <v>12.925170068027</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M24" s="15">
-        <v>16.083916083916</v>
+        <v>15.243902439024</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
         <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>12.5</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" s="15">
-        <v>107.142857142857</v>
+        <v>146.666666666667</v>
       </c>
       <c r="L25" s="15">
-        <v>11.538461538461</v>
+        <v>27.586206896551</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.882352941176</v>
+        <v>17.241379310344</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>9.459459459459</v>
+        <v>15</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.896551724137</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="M26" s="15">
-        <v>-41.726618705036</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>41.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L28" s="15">
-        <v>70</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1500,30 +1500,30 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.226415094339</v>
+        <v>-96.721311475409</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-96</v>
+        <v>-96.491228070175</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>200</v>
+      </c>
+      <c r="I15" s="14">
+        <v>9</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="14">
-        <v>8</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-38.461538461538</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>55.555555555555</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.448275862068</v>
+        <v>-3.125</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.324324324324</v>
+        <v>-22.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.877192982456</v>
+        <v>-49.180327868852</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.331983805668</v>
+        <v>-94.038461538461</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>133.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.126582278481</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="L17" s="15">
-        <v>12.698412698412</v>
+        <v>24.242424242424</v>
       </c>
       <c r="M17" s="15">
-        <v>29.090909090909</v>
+        <v>32.258064516129</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.161434977578</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-60</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.272727272727</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.076923076923</v>
+        <v>-55.714285714285</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.705167173252</v>
+        <v>-91.436464088397</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-87.5</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.518518518518</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.328767123287</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.809523809523</v>
+        <v>-15.730337078651</v>
       </c>
       <c r="M19" s="15">
-        <v>39.130434782608</v>
+        <v>41.509433962264</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.387096774193</v>
+        <v>-44.852941176470</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>92.307692307692</v>
+        <v>70.588235294117</v>
       </c>
       <c r="L20" s="15">
-        <v>19.047619047619</v>
+        <v>38.095238095238</v>
       </c>
       <c r="M20" s="15">
-        <v>-7.407407407407</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.309644670050</v>
+        <v>-85.990338164251</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>2.666666666666</v>
+        <v>3.658536585365</v>
       </c>
       <c r="I21" s="17">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.761904761904</v>
+        <v>-0.772200772200</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.931174089068</v>
+        <v>-1.153846153846</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.728682170542</v>
+        <v>-9.507042253521</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.274481772694</v>
+        <v>-82.934926958831</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>-8.333333333333</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L23" s="15">
-        <v>10</v>
+        <v>19.047619047619</v>
       </c>
       <c r="M23" s="15">
-        <v>57.142857142857</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>155.555555555556</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>39.285714285714</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I24" s="14">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="J24" s="14">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K24" s="15">
-        <v>15.243902439024</v>
+        <v>9.944751381215</v>
       </c>
       <c r="L24" s="15">
-        <v>17.391304347826</v>
+        <v>13.714285714285</v>
       </c>
       <c r="M24" s="15">
-        <v>15.243902439024</v>
+        <v>6.989247311827</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>114.285714285714</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J25" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K25" s="15">
-        <v>146.666666666667</v>
+        <v>129.411764705882</v>
       </c>
       <c r="L25" s="15">
-        <v>27.586206896551</v>
+        <v>30</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>83.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>17.241379310344</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>15</v>
+        <v>14.444444444444</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.075268817204</v>
+        <v>-0.961538461538</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.473684210526</v>
+        <v>-36.024844720496</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>37.5</v>
       </c>
       <c r="L27" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>5</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>15.384615384615</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>58.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.721311475409</v>
+        <v>-97.058823529411</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.491228070175</v>
+        <v>-96.825396825396</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
         <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.125</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.5</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.180327868852</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.038461538461</v>
+        <v>-94.128113879003</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-30.769230769230</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>10.714285714285</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.869565217391</v>
+        <v>-14.423076923076</v>
       </c>
       <c r="L17" s="15">
-        <v>24.242424242424</v>
+        <v>23.611111111111</v>
       </c>
       <c r="M17" s="15">
-        <v>32.258064516129</v>
+        <v>27.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.666666666666</v>
+        <v>-67.279411764705</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14">
         <v>7</v>
       </c>
-      <c r="G18" s="14">
-        <v>11</v>
-      </c>
       <c r="H18" s="15">
-        <v>-36.363636363636</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
         <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.428571428571</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.428571428571</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.714285714285</v>
+        <v>-54.929577464788</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.436464088397</v>
+        <v>-91.959798994974</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
         <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.857142857142</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.597402597402</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.730337078651</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="M19" s="15">
-        <v>41.509433962264</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.852941176470</v>
+        <v>-46.575342465753</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
+        <v>8</v>
+      </c>
+      <c r="G20" s="14">
         <v>7</v>
       </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
       <c r="H20" s="15">
-        <v>75</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>70.588235294117</v>
+        <v>55</v>
       </c>
       <c r="L20" s="15">
-        <v>38.095238095238</v>
+        <v>34.782608695652</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>6.896551724137</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.990338164251</v>
+        <v>-86.462882096069</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.142857142857</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>3.658536585365</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="J21" s="17">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.772200772200</v>
+        <v>-3.202846975088</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.153846153846</v>
+        <v>-3.886925795053</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.507042253521</v>
+        <v>-9.030100334448</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.934926958831</v>
+        <v>-83.454987834549</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-37.5</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>-3.846153846153</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L23" s="15">
-        <v>19.047619047619</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M23" s="15">
-        <v>78.571428571428</v>
+        <v>73.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.529411764705</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H24" s="15">
-        <v>4.545454545454</v>
+        <v>20</v>
       </c>
       <c r="I24" s="14">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="J24" s="14">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="K24" s="15">
-        <v>9.944751381215</v>
+        <v>11.224489795918</v>
       </c>
       <c r="L24" s="15">
-        <v>13.714285714285</v>
+        <v>15.957446808510</v>
       </c>
       <c r="M24" s="15">
-        <v>6.989247311827</v>
+        <v>7.920792079207</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K25" s="15">
-        <v>129.411764705882</v>
+        <v>115.789473684211</v>
       </c>
       <c r="L25" s="15">
-        <v>30</v>
+        <v>20.588235294117</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>5.555555555555</v>
+        <v>26.470588235294</v>
       </c>
       <c r="I26" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K26" s="15">
-        <v>14.444444444444</v>
+        <v>15.306122448979</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.961538461538</v>
+        <v>1.801801801801</v>
       </c>
       <c r="M26" s="15">
-        <v>-36.024844720496</v>
+        <v>-35.057471264367</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>5</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>150</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>46.153846153846</v>
+        <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>58.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-85.714285714285</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.058823529411</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.825396825396</v>
+        <v>-96.923076923076</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -920,13 +920,13 @@
         <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-43.75</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>8.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.941176470588</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.428571428571</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.619047619047</v>
+        <v>-43.283582089552</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.128113879003</v>
+        <v>-93.613445378151</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,10 +975,10 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
         <v>-50</v>
@@ -987,69 +987,69 @@
         <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I17" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J17" s="14">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.423076923076</v>
+        <v>-17.543859649122</v>
       </c>
       <c r="L17" s="15">
-        <v>23.611111111111</v>
+        <v>23.684210526315</v>
       </c>
       <c r="M17" s="15">
-        <v>27.142857142857</v>
+        <v>27.027027027027</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.279411764705</v>
+        <v>-68.350168350168</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.571428571428</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.789473684210</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.929577464788</v>
+        <v>-52</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.959798994974</v>
+        <v>-91.627906976744</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.428571428571</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.878048780487</v>
+        <v>-5.681818181818</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.408163265306</v>
+        <v>-16.161616161616</v>
       </c>
       <c r="M19" s="15">
-        <v>36.842105263157</v>
+        <v>23.880597014925</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.575342465753</v>
+        <v>-47.133757961783</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>14.285714285714</v>
+        <v>-30</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
-        <v>55</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L20" s="15">
-        <v>34.782608695652</v>
+        <v>39.130434782608</v>
       </c>
       <c r="M20" s="15">
-        <v>6.896551724137</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.462882096069</v>
+        <v>-86.991869918699</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.363636363636</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.333333333333</v>
+        <v>-14.606741573033</v>
       </c>
       <c r="I21" s="17">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="J21" s="17">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.202846975088</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.886925795053</v>
+        <v>-1.351351351351</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.030100334448</v>
+        <v>-9.316770186335</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.454987834549</v>
+        <v>-83.456090651558</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L23" s="15">
-        <v>13.043478260869</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M23" s="15">
-        <v>73.333333333333</v>
+        <v>80</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
         <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>20</v>
+        <v>26.785714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J24" s="14">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K24" s="15">
-        <v>11.224489795918</v>
+        <v>11.374407582938</v>
       </c>
       <c r="L24" s="15">
-        <v>15.957446808510</v>
+        <v>17.5</v>
       </c>
       <c r="M24" s="15">
-        <v>7.920792079207</v>
+        <v>6.818181818181</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>116.666666666667</v>
+        <v>150</v>
       </c>
       <c r="I25" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>115.789473684211</v>
+        <v>120</v>
       </c>
       <c r="L25" s="15">
-        <v>20.588235294117</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>37.5</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G26" s="14">
         <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>26.470588235294</v>
+        <v>8.823529411764</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K26" s="15">
-        <v>15.306122448979</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>1.801801801801</v>
+        <v>0.862068965517</v>
       </c>
       <c r="M26" s="15">
-        <v>-35.057471264367</v>
+        <v>-41.206030150753</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>-9.090909090909</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>60</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.142857142857</v>
+        <v>-97.297297297297</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-84.615384615384</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.923076923076</v>
+        <v>-97.101449275362</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.058823529411</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>55.555555555555</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>8.571428571428</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.555555555555</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.283582089552</v>
+        <v>-42.253521126760</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.613445378151</v>
+        <v>-93.512658227848</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>62.5</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.315789473684</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I17" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J17" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.543859649122</v>
+        <v>-12.295081967213</v>
       </c>
       <c r="L17" s="15">
-        <v>23.684210526315</v>
+        <v>21.590909090909</v>
       </c>
       <c r="M17" s="15">
-        <v>27.027027027027</v>
+        <v>40.789473684210</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.350168350168</v>
+        <v>-66.246056782334</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.263157894736</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M18" s="15">
-        <v>-52</v>
+        <v>-50.649350649350</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.627906976744</v>
+        <v>-91.684901531728</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.739130434782</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I19" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.681818181818</v>
+        <v>-8.421052631578</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.161616161616</v>
+        <v>-16.346153846153</v>
       </c>
       <c r="M19" s="15">
-        <v>23.880597014925</v>
+        <v>19.178082191780</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.133757961783</v>
+        <v>-48.823529411764</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-30</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I20" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>39.130434782608</v>
+        <v>29.629629629629</v>
       </c>
       <c r="L20" s="15">
-        <v>39.130434782608</v>
+        <v>45.833333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>6.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.991869918699</v>
+        <v>-86.742424242424</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.606741573033</v>
+        <v>-11.224489795918</v>
       </c>
       <c r="I21" s="17">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="J21" s="17">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.947368421052</v>
+        <v>-3.647416413373</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.351351351351</v>
+        <v>-0.314465408805</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.316770186335</v>
+        <v>-5.934718100890</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.456090651558</v>
+        <v>-83.156216790648</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="15">
         <v>-66.666666666666</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F23" s="14">
+        <v>8</v>
+      </c>
+      <c r="G23" s="14">
+        <v>9</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="I23" s="14">
+        <v>30</v>
+      </c>
+      <c r="J23" s="14">
+        <v>33</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L23" s="15">
+        <v>7.142857142857</v>
+      </c>
+      <c r="M23" s="15">
         <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>5</v>
-      </c>
-      <c r="G23" s="14">
-        <v>5</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
-      </c>
-      <c r="I23" s="14">
-        <v>27</v>
-      </c>
-      <c r="J23" s="14">
-        <v>29</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-6.896551724137</v>
-      </c>
-      <c r="L23" s="15">
-        <v>3.846153846153</v>
-      </c>
-      <c r="M23" s="15">
-        <v>80</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>23</v>
+      </c>
+      <c r="D24" s="14">
         <v>17</v>
       </c>
-      <c r="D24" s="14">
-        <v>15</v>
-      </c>
       <c r="E24" s="15">
-        <v>13.333333333333</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>26.785714285714</v>
+        <v>14.0625</v>
       </c>
       <c r="I24" s="14">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="J24" s="14">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="K24" s="15">
-        <v>11.374407582938</v>
+        <v>13.157894736842</v>
       </c>
       <c r="L24" s="15">
-        <v>17.5</v>
+        <v>21.126760563380</v>
       </c>
       <c r="M24" s="15">
-        <v>6.818181818181</v>
+        <v>10.256410256410</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>1</v>
-      </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L25" s="15">
-        <v>22.222222222222</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>8.823529411764</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J26" s="14">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K26" s="15">
-        <v>8.333333333333</v>
+        <v>14.655172413793</v>
       </c>
       <c r="L26" s="15">
-        <v>0.862068965517</v>
+        <v>4.724409448818</v>
       </c>
       <c r="M26" s="15">
-        <v>-41.206030150753</v>
+        <v>-37.264150943396</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
         <v>-33.333333333333</v>
@@ -1429,10 +1429,10 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
@@ -1444,16 +1444,16 @@
         <v>180</v>
       </c>
       <c r="I28" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>52.941176470588</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>85.714285714285</v>
+        <v>86.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.297297297297</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.101449275362</v>
+        <v>-97.183098591549</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
+      <c r="H15" s="15">
         <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="15">
-        <v>50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
         <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>10.810810810810</v>
+        <v>18.918918918918</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.583333333333</v>
+        <v>-12</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.253521126760</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.512658227848</v>
+        <v>-93.442622950819</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>62.5</v>
+        <v>-55</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.930232558139</v>
+        <v>-24</v>
       </c>
       <c r="I17" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J17" s="14">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.295081967213</v>
+        <v>-14.788732394366</v>
       </c>
       <c r="L17" s="15">
-        <v>21.590909090909</v>
+        <v>27.368421052631</v>
       </c>
       <c r="M17" s="15">
-        <v>40.789473684210</v>
+        <v>44.047619047619</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.246056782334</v>
+        <v>-64.927536231884</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>11.111111111111</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.317073170731</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.317073170731</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="M18" s="15">
-        <v>-50.649350649350</v>
+        <v>-51.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.684901531728</v>
+        <v>-91.848906560636</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.421052631578</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.346153846153</v>
+        <v>-12.389380530973</v>
       </c>
       <c r="M19" s="15">
-        <v>19.178082191780</v>
+        <v>32</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.823529411764</v>
+        <v>-46.195652173913</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>29.629629629629</v>
+        <v>27.586206896551</v>
       </c>
       <c r="L20" s="15">
-        <v>45.833333333333</v>
+        <v>54.166666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>2.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.742424242424</v>
+        <v>-86.832740213523</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.224489795918</v>
+        <v>-8.910891089108</v>
       </c>
       <c r="I21" s="17">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="J21" s="17">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.647416413373</v>
+        <v>-2.5</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.314465408805</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.934718100890</v>
+        <v>-3.835616438356</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.156216790648</v>
+        <v>-82.683769116921</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,10 +1201,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L22" s="15">
         <v>-66.666666666666</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
+        <v>7</v>
+      </c>
+      <c r="G23" s="14">
         <v>8</v>
       </c>
-      <c r="G23" s="14">
-        <v>9</v>
-      </c>
       <c r="H23" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.090909090909</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L23" s="15">
-        <v>7.142857142857</v>
+        <v>10.344827586206</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>35.294117647058</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F24" s="14">
         <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>14.0625</v>
+        <v>30.357142857142</v>
       </c>
       <c r="I24" s="14">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="J24" s="14">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="K24" s="15">
-        <v>13.157894736842</v>
+        <v>13.924050632911</v>
       </c>
       <c r="L24" s="15">
-        <v>21.126760563380</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M24" s="15">
-        <v>10.256410256410</v>
+        <v>8.870967741935</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
         <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K25" s="15">
-        <v>100</v>
+        <v>91.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>21.052631578947</v>
+        <v>17.948717948717</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="I26" s="14">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J26" s="14">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="K26" s="15">
-        <v>14.655172413793</v>
+        <v>7.874015748031</v>
       </c>
       <c r="L26" s="15">
-        <v>4.724409448818</v>
+        <v>3.007518796992</v>
       </c>
       <c r="M26" s="15">
-        <v>-37.264150943396</v>
+        <v>-42.436974789916</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
+      <c r="H27" s="15">
         <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>55.555555555555</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L28" s="15">
-        <v>86.666666666666</v>
+        <v>81.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-90.909090909090</v>
+        <v>-86.363636363636</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.368421052631</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-88.235294117647</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.183098591549</v>
+        <v>-96.052631578947</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -926,7 +926,7 @@
         <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>18.918918918918</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L16" s="15">
-        <v>-12</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.540540540540</v>
+        <v>-36.708860759493</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.442622950819</v>
+        <v>-93.084370677731</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
         <v>9</v>
       </c>
-      <c r="D17" s="14">
-        <v>20</v>
-      </c>
       <c r="E17" s="15">
-        <v>-55</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H17" s="15">
-        <v>-24</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="I17" s="14">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J17" s="14">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.788732394366</v>
+        <v>-14.569536423841</v>
       </c>
       <c r="L17" s="15">
-        <v>27.368421052631</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M17" s="15">
-        <v>44.047619047619</v>
+        <v>35.789473684210</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.927536231884</v>
+        <v>-64.560439560439</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>-4.651162790697</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.380952380952</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M18" s="15">
-        <v>-51.764705882352</v>
+        <v>-52.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.848906560636</v>
+        <v>-91.886792452830</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
         <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.941176470588</v>
+        <v>-3.603603603603</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.389380530973</v>
+        <v>-10.833333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>32</v>
+        <v>30.487804878048</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.195652173913</v>
+        <v>-44.270833333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K20" s="15">
-        <v>27.586206896551</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>54.166666666666</v>
+        <v>59.259259259259</v>
       </c>
       <c r="M20" s="15">
-        <v>2.777777777777</v>
+        <v>10.256410256410</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.832740213523</v>
+        <v>-85.423728813559</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.258064516129</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="F21" s="17">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.910891089108</v>
+        <v>-8.849557522123</v>
       </c>
       <c r="I21" s="17">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="J21" s="17">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.5</v>
+        <v>-3.299492385786</v>
       </c>
       <c r="L21" s="18">
-        <v>3.846153846153</v>
+        <v>5.248618784530</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.835616438356</v>
+        <v>-3.787878787878</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.683769116921</v>
+        <v>-82.279069767441</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I22" s="14">
         <v>3</v>
       </c>
-      <c r="H22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>2</v>
-      </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="L22" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>-81.818181818181</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
+        <v>10</v>
+      </c>
+      <c r="G23" s="14">
         <v>7</v>
       </c>
-      <c r="G23" s="14">
-        <v>8</v>
-      </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I23" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J23" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>10.344827586206</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>77.777777777777</v>
+        <v>59.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>77.777777777777</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H24" s="15">
-        <v>30.357142857142</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I24" s="14">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="J24" s="14">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="K24" s="15">
-        <v>13.924050632911</v>
+        <v>10.629921259842</v>
       </c>
       <c r="L24" s="15">
-        <v>22.727272727272</v>
+        <v>21.120689655172</v>
       </c>
       <c r="M24" s="15">
-        <v>8.870967741935</v>
+        <v>4.074074074074</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>91.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="L25" s="15">
-        <v>17.948717948717</v>
+        <v>17.073170731707</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.702702702702</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I26" s="14">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="J26" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K26" s="15">
-        <v>7.874015748031</v>
+        <v>12.5</v>
       </c>
       <c r="L26" s="15">
-        <v>3.007518796992</v>
+        <v>7.746478873239</v>
       </c>
       <c r="M26" s="15">
-        <v>-42.436974789916</v>
+        <v>-42.045454545454</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>38.095238095238</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>81.25</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-86.363636363636</v>
+        <v>-86.956521739130</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-82.352941176470</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.052631578947</v>
+        <v>-96.202531645569</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-077pct.xlsx
+++ b/data/source/weekly/cs-en-us-077pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-55</v>
+        <v>-52.380952380952</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>19.047619047619</v>
+        <v>15.217391304347</v>
       </c>
       <c r="L16" s="15">
-        <v>-5.660377358490</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.708860759493</v>
+        <v>-35.365853658536</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.084370677731</v>
+        <v>-93.053735255570</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
         <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G17" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.404255319148</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="I17" s="14">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.569536423841</v>
+        <v>-12.5</v>
       </c>
       <c r="L17" s="15">
-        <v>26.470588235294</v>
+        <v>29.629629629629</v>
       </c>
       <c r="M17" s="15">
-        <v>35.789473684210</v>
+        <v>41.414141414141</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.560439560439</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.416666666666</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.521739130434</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.222222222222</v>
+        <v>-52.577319587628</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.886792452830</v>
+        <v>-91.915641476274</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
         <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.603603603603</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.833333333333</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="M19" s="15">
-        <v>30.487804878048</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.270833333333</v>
+        <v>-41.176470588235</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I20" s="14">
         <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>22.857142857142</v>
+        <v>19.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>59.259259259259</v>
+        <v>48.275862068965</v>
       </c>
       <c r="M20" s="15">
-        <v>10.256410256410</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.423728813559</v>
+        <v>-85.855263157894</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.705882352941</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.849557522123</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="I21" s="17">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="J21" s="17">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.299492385786</v>
+        <v>-0.722891566265</v>
       </c>
       <c r="L21" s="18">
-        <v>5.248618784530</v>
+        <v>6.459948320413</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.787878787878</v>
+        <v>-2.137767220902</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.279069767441</v>
+        <v>-81.866197183098</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>-72.727272727272</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>4</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
         <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>42.857142857142</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>16.666666666666</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>59.090909090909</v>
+        <v>56.521739130434</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.647058823529</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F24" s="14">
         <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>10.344827586206</v>
+        <v>4.918032786885</v>
       </c>
       <c r="I24" s="14">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="J24" s="14">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K24" s="15">
-        <v>10.629921259842</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L24" s="15">
-        <v>21.120689655172</v>
+        <v>21.810699588477</v>
       </c>
       <c r="M24" s="15">
-        <v>4.074074074074</v>
+        <v>2.777777777777</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
         <v>7</v>
@@ -1321,16 +1321,16 @@
         <v>-12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>77.777777777777</v>
+        <v>82.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>17.073170731707</v>
+        <v>10.869565217391</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>55.555555555555</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>5.263157894736</v>
+        <v>28.205128205128</v>
       </c>
       <c r="I26" s="14">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J26" s="14">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>12.5</v>
+        <v>13.605442176870</v>
       </c>
       <c r="L26" s="15">
-        <v>7.746478873239</v>
+        <v>10.596026490066</v>
       </c>
       <c r="M26" s="15">
-        <v>-42.045454545454</v>
+        <v>-40.989399293286</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,22 +1438,22 @@
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>36.363636363636</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-86.956521739130</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.428571428571</v>
+        <v>-96.629213483146</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.202531645569</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
